--- a/gerber/PickAndPlace_PCB1_2026_07_11.xlsx
+++ b/gerber/PickAndPlace_PCB1_2026_07_11.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB1_2026_07_11" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB1_2026_07_15" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="203">
   <si>
     <t>Designator</t>
   </si>
@@ -67,13 +67,13 @@
     <t>C0805</t>
   </si>
   <si>
-    <t>16.383mm</t>
-  </si>
-  <si>
-    <t>-46.482mm</t>
-  </si>
-  <si>
-    <t>17.383mm</t>
+    <t>18.923mm</t>
+  </si>
+  <si>
+    <t>-49.911mm</t>
+  </si>
+  <si>
+    <t>19.923mm</t>
   </si>
   <si>
     <t>T</t>
@@ -106,9 +106,6 @@
     <t>C3</t>
   </si>
   <si>
-    <t>18.923mm</t>
-  </si>
-  <si>
     <t>-30.353mm</t>
   </si>
   <si>
@@ -166,439 +163,463 @@
     <t>28.829mm</t>
   </si>
   <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>5.08mm</t>
+  </si>
+  <si>
+    <t>-13.208mm</t>
+  </si>
+  <si>
+    <t>6.08mm</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>40.386mm</t>
+  </si>
+  <si>
+    <t>-33.274mm</t>
+  </si>
+  <si>
+    <t>-34.274mm</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>37.846mm</t>
+  </si>
+  <si>
+    <t>-26.67mm</t>
+  </si>
+  <si>
+    <t>36.846mm</t>
+  </si>
+  <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>CAP_0603</t>
+  </si>
+  <si>
+    <t>C0603</t>
+  </si>
+  <si>
+    <t>11.049mm</t>
+  </si>
+  <si>
+    <t>-33.655mm</t>
+  </si>
+  <si>
+    <t>11.749mm</t>
+  </si>
+  <si>
+    <t>1µF</t>
+  </si>
+  <si>
+    <t>CN1</t>
+  </si>
+  <si>
+    <t>DB128L-5.08-4P-GN-S</t>
+  </si>
+  <si>
+    <t>CONN-TH_4P_DB128L-5.08-4P-GN-S</t>
+  </si>
+  <si>
+    <t>26.416mm</t>
+  </si>
+  <si>
+    <t>-5.969mm</t>
+  </si>
+  <si>
+    <t>34.036mm</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>MHCI06024-100M-R8A</t>
+  </si>
+  <si>
+    <t>IND-SMD_L7.3-W6.6</t>
+  </si>
+  <si>
+    <t>7.62mm</t>
+  </si>
+  <si>
+    <t>-6.35mm</t>
+  </si>
+  <si>
+    <t>-3.072mm</t>
+  </si>
+  <si>
+    <t>10uH</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>-17.272mm</t>
+  </si>
+  <si>
+    <t>-20.55mm</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>-20.296mm</t>
+  </si>
+  <si>
+    <t>L4</t>
+  </si>
+  <si>
+    <t>44.704mm</t>
+  </si>
+  <si>
+    <t>-6.477mm</t>
+  </si>
+  <si>
+    <t>-9.755mm</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>Res_0603</t>
+  </si>
+  <si>
+    <t>R0603</t>
+  </si>
+  <si>
+    <t>20.955mm</t>
+  </si>
+  <si>
+    <t>-36.449mm</t>
+  </si>
+  <si>
+    <t>-37.202mm</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>23.749mm</t>
+  </si>
+  <si>
+    <t>15K</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>18.669mm</t>
+  </si>
+  <si>
+    <t>-41.148mm</t>
+  </si>
+  <si>
+    <t>19.422mm</t>
+  </si>
+  <si>
+    <t>10K</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>-43.561mm</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>18.542mm</t>
+  </si>
+  <si>
+    <t>-46.101mm</t>
+  </si>
+  <si>
+    <t>19.295mm</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>32.528mm</t>
+  </si>
+  <si>
+    <t>-38.563mm</t>
+  </si>
+  <si>
+    <t>-37.809mm</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>15.494mm</t>
+  </si>
+  <si>
+    <t>-36.322mm</t>
+  </si>
+  <si>
+    <t>-37.075mm</t>
+  </si>
+  <si>
+    <t>4.7K</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>18.161mm</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>TAS5825MRHBR</t>
+  </si>
+  <si>
+    <t>VQFN-32_L5.0-W5.0-P0.50-TL-EP</t>
+  </si>
+  <si>
+    <t>28.027mm</t>
+  </si>
+  <si>
+    <t>-32.582mm</t>
+  </si>
+  <si>
+    <t>25.62mm</t>
+  </si>
+  <si>
+    <t>-30.832mm</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>B7B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>CONN-TH_7P-P2.50_B7B-XH-A-LF-SN</t>
+  </si>
+  <si>
+    <t>25.4mm</t>
+  </si>
+  <si>
+    <t>-55.118mm</t>
+  </si>
+  <si>
+    <t>17.9mm</t>
+  </si>
+  <si>
+    <t>-55.119mm</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>MM1Z15_C115219</t>
+  </si>
+  <si>
+    <t>SOD-123_L2.8-W1.8-LS3.7-RD</t>
+  </si>
+  <si>
+    <t>48.133mm</t>
+  </si>
+  <si>
+    <t>-42.672mm</t>
+  </si>
+  <si>
+    <t>-40.98mm</t>
+  </si>
+  <si>
+    <t>MM1Z15</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>AO4407A_C16072</t>
+  </si>
+  <si>
+    <t>SOIC-8_L4.9-W3.9-P1.27-LS6.0-BL</t>
+  </si>
+  <si>
+    <t>43.561mm</t>
+  </si>
+  <si>
+    <t>-42.799mm</t>
+  </si>
+  <si>
+    <t>41.656mm</t>
+  </si>
+  <si>
+    <t>-45.369mm</t>
+  </si>
+  <si>
+    <t>AO4407A</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>51.562mm</t>
+  </si>
+  <si>
+    <t>-42.037mm</t>
+  </si>
+  <si>
+    <t>-42.79mm</t>
+  </si>
+  <si>
+    <t>100K</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>DB128L-5.08-2P-GN-S</t>
+  </si>
+  <si>
+    <t>CONN-TH_2P-P5.08_DB128L-5.08-2P</t>
+  </si>
+  <si>
+    <t>42.799mm</t>
+  </si>
+  <si>
+    <t>-53.721mm</t>
+  </si>
+  <si>
+    <t>45.339mm</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>GR226M050D11RR0VH4FP0</t>
+  </si>
+  <si>
+    <t>CAP-TH_BD5.0-P2.00-D0.8-FD</t>
+  </si>
+  <si>
+    <t>43.815mm</t>
+  </si>
+  <si>
+    <t>-29.591mm</t>
+  </si>
+  <si>
+    <t>-28.591mm</t>
+  </si>
+  <si>
+    <t>22uF</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>35.433mm</t>
+  </si>
+  <si>
+    <t>-33.909mm</t>
+  </si>
+  <si>
+    <t>34.433mm</t>
+  </si>
+  <si>
+    <t>C13</t>
+  </si>
+  <si>
+    <t>36.83mm</t>
+  </si>
+  <si>
+    <t>35.83mm</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>5.207mm</t>
+  </si>
+  <si>
+    <t>-25.4mm</t>
+  </si>
+  <si>
+    <t>4.207mm</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>9.779mm</t>
+  </si>
+  <si>
+    <t>-40.767mm</t>
+  </si>
+  <si>
+    <t>10.779mm</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>-18.669mm</t>
+  </si>
+  <si>
+    <t>4.08mm</t>
+  </si>
+  <si>
+    <t>C21</t>
+  </si>
+  <si>
+    <t>49.276mm</t>
+  </si>
+  <si>
+    <t>-32.274mm</t>
+  </si>
+  <si>
     <t>C9</t>
   </si>
   <si>
-    <t>CAP_0603</t>
-  </si>
-  <si>
-    <t>C0603</t>
-  </si>
-  <si>
-    <t>48.133mm</t>
-  </si>
-  <si>
-    <t>-33.147mm</t>
-  </si>
-  <si>
-    <t>-32.447mm</t>
-  </si>
-  <si>
-    <t>390µF</t>
-  </si>
-  <si>
-    <t>C10</t>
-  </si>
-  <si>
-    <t>43.485mm</t>
-  </si>
-  <si>
-    <t>-33.078mm</t>
-  </si>
-  <si>
-    <t>-32.378mm</t>
-  </si>
-  <si>
-    <t>22µF</t>
-  </si>
-  <si>
-    <t>C11</t>
-  </si>
-  <si>
-    <t>5.399mm</t>
-  </si>
-  <si>
-    <t>-26.597mm</t>
-  </si>
-  <si>
-    <t>6.399mm</t>
-  </si>
-  <si>
-    <t>C12</t>
-  </si>
-  <si>
-    <t>35.433mm</t>
-  </si>
-  <si>
-    <t>-33.909mm</t>
-  </si>
-  <si>
-    <t>34.733mm</t>
-  </si>
-  <si>
-    <t>C13</t>
-  </si>
-  <si>
-    <t>-36.068mm</t>
+    <t>BXJ 35V390 10*10</t>
+  </si>
+  <si>
+    <t>CAP-SMD_BD10.0-L10.3-W10.3-FD</t>
+  </si>
+  <si>
+    <t>46.609mm</t>
+  </si>
+  <si>
+    <t>-18.542mm</t>
+  </si>
+  <si>
+    <t>-14.042mm</t>
+  </si>
+  <si>
+    <t>390uF</t>
   </si>
   <si>
     <t>C14</t>
   </si>
   <si>
-    <t>5.207mm</t>
-  </si>
-  <si>
-    <t>4.507mm</t>
-  </si>
-  <si>
-    <t>C15</t>
-  </si>
-  <si>
-    <t>5.152mm</t>
-  </si>
-  <si>
-    <t>-23.803mm</t>
-  </si>
-  <si>
-    <t>4.452mm</t>
-  </si>
-  <si>
-    <t>C16</t>
-  </si>
-  <si>
-    <t>40.386mm</t>
-  </si>
-  <si>
-    <t>-33.274mm</t>
-  </si>
-  <si>
-    <t>-34.274mm</t>
-  </si>
-  <si>
-    <t>C17</t>
-  </si>
-  <si>
-    <t>37.846mm</t>
-  </si>
-  <si>
-    <t>-26.67mm</t>
-  </si>
-  <si>
-    <t>36.846mm</t>
-  </si>
-  <si>
-    <t>C18</t>
-  </si>
-  <si>
-    <t>-30.861mm</t>
-  </si>
-  <si>
-    <t>4,7µF</t>
-  </si>
-  <si>
-    <t>C19</t>
-  </si>
-  <si>
-    <t>10.922mm</t>
-  </si>
-  <si>
-    <t>-30.734mm</t>
-  </si>
-  <si>
-    <t>11.622mm</t>
-  </si>
-  <si>
-    <t>1µF</t>
-  </si>
-  <si>
-    <t>C20</t>
-  </si>
-  <si>
-    <t>-20.701mm</t>
-  </si>
-  <si>
-    <t>C21</t>
-  </si>
-  <si>
-    <t>45.749mm</t>
-  </si>
-  <si>
-    <t>CN1</t>
-  </si>
-  <si>
-    <t>DB128L-5.08-4P-GN-S</t>
-  </si>
-  <si>
-    <t>CONN-TH_4P_DB128L-5.08-4P-GN-S</t>
-  </si>
-  <si>
-    <t>26.416mm</t>
-  </si>
-  <si>
-    <t>-5.969mm</t>
-  </si>
-  <si>
-    <t>34.036mm</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>MHCI06024-100M-R8A</t>
-  </si>
-  <si>
-    <t>IND-SMD_L7.3-W6.6</t>
-  </si>
-  <si>
-    <t>7.62mm</t>
-  </si>
-  <si>
-    <t>-6.35mm</t>
-  </si>
-  <si>
-    <t>-3.072mm</t>
-  </si>
-  <si>
-    <t>10uH</t>
-  </si>
-  <si>
-    <t>L2</t>
-  </si>
-  <si>
-    <t>-17.272mm</t>
-  </si>
-  <si>
-    <t>-20.55mm</t>
-  </si>
-  <si>
-    <t>L3</t>
-  </si>
-  <si>
-    <t>-20.296mm</t>
-  </si>
-  <si>
-    <t>L4</t>
-  </si>
-  <si>
-    <t>44.704mm</t>
-  </si>
-  <si>
-    <t>-6.477mm</t>
-  </si>
-  <si>
-    <t>-9.755mm</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>Res_0603</t>
-  </si>
-  <si>
-    <t>R0603</t>
-  </si>
-  <si>
-    <t>9.928mm</t>
-  </si>
-  <si>
-    <t>-45.665mm</t>
-  </si>
-  <si>
-    <t>-46.418mm</t>
-  </si>
-  <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>12.827mm</t>
-  </si>
-  <si>
-    <t>-45.72mm</t>
-  </si>
-  <si>
-    <t>-46.473mm</t>
-  </si>
-  <si>
-    <t>15K</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>18.415mm</t>
-  </si>
-  <si>
-    <t>-38.1mm</t>
-  </si>
-  <si>
-    <t>19.168mm</t>
-  </si>
-  <si>
-    <t>10K</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>-40.513mm</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>18.288mm</t>
-  </si>
-  <si>
-    <t>-43.053mm</t>
-  </si>
-  <si>
-    <t>19.041mm</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>32.528mm</t>
-  </si>
-  <si>
-    <t>-38.563mm</t>
-  </si>
-  <si>
-    <t>-37.809mm</t>
-  </si>
-  <si>
-    <t>R7</t>
-  </si>
-  <si>
-    <t>4.22mm</t>
-  </si>
-  <si>
-    <t>4.7K</t>
-  </si>
-  <si>
-    <t>R8</t>
-  </si>
-  <si>
-    <t>7.077mm</t>
-  </si>
-  <si>
-    <t>-46.474mm</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>TAS5825MRHBR</t>
-  </si>
-  <si>
-    <t>VQFN-32_L5.0-W5.0-P0.50-TL-EP</t>
-  </si>
-  <si>
-    <t>28.027mm</t>
-  </si>
-  <si>
-    <t>-32.582mm</t>
-  </si>
-  <si>
-    <t>25.62mm</t>
-  </si>
-  <si>
-    <t>-30.832mm</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>B7B-XH-A(LF)(SN)</t>
-  </si>
-  <si>
-    <t>CONN-TH_7P-P2.50_B7B-XH-A-LF-SN</t>
-  </si>
-  <si>
-    <t>25.4mm</t>
-  </si>
-  <si>
-    <t>-55.118mm</t>
-  </si>
-  <si>
-    <t>17.9mm</t>
-  </si>
-  <si>
-    <t>-55.119mm</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>MM1Z15_C115219</t>
-  </si>
-  <si>
-    <t>SOD-123_L2.8-W1.8-LS3.7-RD</t>
-  </si>
-  <si>
-    <t>45.212mm</t>
-  </si>
-  <si>
-    <t>-39.116mm</t>
-  </si>
-  <si>
-    <t>43.52mm</t>
-  </si>
-  <si>
-    <t>MM1Z15</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>AO4407A_C16072</t>
-  </si>
-  <si>
-    <t>SOIC-8_L4.9-W3.9-P1.27-LS6.0-BL</t>
-  </si>
-  <si>
-    <t>45.339mm</t>
-  </si>
-  <si>
-    <t>47.244mm</t>
-  </si>
-  <si>
-    <t>-43.912mm</t>
-  </si>
-  <si>
-    <t>AO4407A</t>
-  </si>
-  <si>
-    <t>R9</t>
-  </si>
-  <si>
-    <t>36.957mm</t>
-  </si>
-  <si>
-    <t>-43.815mm</t>
-  </si>
-  <si>
-    <t>36.204mm</t>
-  </si>
-  <si>
-    <t>100K</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>DB128L-5.08-2P-GN-S</t>
-  </si>
-  <si>
-    <t>CONN-TH_2P-P5.08_DB128L-5.08-2P</t>
-  </si>
-  <si>
-    <t>46.99mm</t>
-  </si>
-  <si>
-    <t>-21.082mm</t>
-  </si>
-  <si>
-    <t>-18.542mm</t>
+    <t>7.747mm</t>
+  </si>
+  <si>
+    <t>3.247mm</t>
   </si>
 </sst>
 </file>
@@ -1133,22 +1154,22 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
         <v>31</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
         <v>32</v>
-      </c>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" t="s">
-        <v>33</v>
       </c>
       <c r="J4">
         <v>2</v>
@@ -1163,15 +1184,15 @@
         <v>22</v>
       </c>
       <c r="N4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1180,22 +1201,22 @@
         <v>17</v>
       </c>
       <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
         <v>36</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
         <v>37</v>
-      </c>
-      <c r="F5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" t="s">
-        <v>38</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -1218,7 +1239,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1227,22 +1248,22 @@
         <v>17</v>
       </c>
       <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" t="s">
         <v>41</v>
       </c>
-      <c r="F6" t="s">
+      <c r="I6" t="s">
         <v>40</v>
-      </c>
-      <c r="G6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" t="s">
-        <v>41</v>
       </c>
       <c r="J6">
         <v>2</v>
@@ -1257,15 +1278,15 @@
         <v>22</v>
       </c>
       <c r="N6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -1274,19 +1295,19 @@
         <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G7" t="s">
         <v>27</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I7" t="s">
         <v>28</v>
@@ -1312,7 +1333,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
@@ -1321,22 +1342,22 @@
         <v>17</v>
       </c>
       <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
         <v>46</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" t="s">
         <v>47</v>
       </c>
-      <c r="F8" t="s">
+      <c r="I8" t="s">
         <v>46</v>
-      </c>
-      <c r="G8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" t="s">
-        <v>47</v>
       </c>
       <c r="J8">
         <v>2</v>
@@ -1351,15 +1372,15 @@
         <v>22</v>
       </c>
       <c r="N8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
@@ -1368,22 +1389,22 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" t="s">
         <v>37</v>
-      </c>
-      <c r="F9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" t="s">
-        <v>38</v>
       </c>
       <c r="J9">
         <v>2</v>
@@ -1406,31 +1427,31 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
         <v>51</v>
       </c>
-      <c r="B10" t="s">
+      <c r="E10" t="s">
         <v>52</v>
       </c>
-      <c r="C10" t="s">
+      <c r="F10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" t="s">
         <v>53</v>
       </c>
-      <c r="D10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10" t="s">
-        <v>54</v>
-      </c>
       <c r="I10" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J10">
         <v>2</v>
@@ -1439,45 +1460,45 @@
         <v>21</v>
       </c>
       <c r="L10">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M10" t="s">
         <v>22</v>
       </c>
       <c r="N10" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="O10" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J11">
         <v>2</v>
@@ -1486,45 +1507,45 @@
         <v>21</v>
       </c>
       <c r="L11">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M11" t="s">
         <v>22</v>
       </c>
       <c r="N11" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="O11" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H12" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I12" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -1533,45 +1554,45 @@
         <v>21</v>
       </c>
       <c r="L12">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
         <v>22</v>
       </c>
       <c r="N12" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="O12" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" t="s">
         <v>67</v>
       </c>
-      <c r="B13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G13" t="s">
-        <v>69</v>
-      </c>
-      <c r="H13" t="s">
-        <v>70</v>
-      </c>
       <c r="I13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -1580,48 +1601,48 @@
         <v>21</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M13" t="s">
         <v>22</v>
       </c>
       <c r="N13" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O13" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" t="s">
         <v>71</v>
       </c>
-      <c r="B14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" t="s">
-        <v>53</v>
-      </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" t="s">
         <v>72</v>
       </c>
-      <c r="F14" t="s">
-        <v>68</v>
-      </c>
       <c r="G14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K14" t="s">
         <v>21</v>
@@ -1630,42 +1651,42 @@
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="N14" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="O14" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -1674,45 +1695,45 @@
         <v>21</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M15" t="s">
         <v>22</v>
       </c>
       <c r="N15" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="O15" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F16" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="G16" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H16" t="s">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J16">
         <v>2</v>
@@ -1721,45 +1742,45 @@
         <v>21</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M16" t="s">
         <v>22</v>
       </c>
       <c r="N16" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="O16" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="H17" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I17" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J17">
         <v>2</v>
@@ -1768,45 +1789,45 @@
         <v>21</v>
       </c>
       <c r="L17">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M17" t="s">
         <v>22</v>
       </c>
       <c r="N17" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="O17" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F18" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G18" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I18" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J18">
         <v>2</v>
@@ -1815,45 +1836,45 @@
         <v>21</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M18" t="s">
         <v>22</v>
       </c>
       <c r="N18" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="O18" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="E19" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="G19" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="H19" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="I19" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="J19">
         <v>2</v>
@@ -1862,45 +1883,45 @@
         <v>21</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M19" t="s">
         <v>22</v>
       </c>
       <c r="N19" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="O19" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F20" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H20" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I20" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J20">
         <v>2</v>
@@ -1909,45 +1930,45 @@
         <v>21</v>
       </c>
       <c r="L20">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M20" t="s">
         <v>22</v>
       </c>
       <c r="N20" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="O20" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F21" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="G21" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H21" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="I21" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="J21">
         <v>2</v>
@@ -1956,45 +1977,45 @@
         <v>21</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M21" t="s">
         <v>22</v>
       </c>
       <c r="N21" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="O21" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="F22" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G22" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="H22" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I22" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="J22">
         <v>2</v>
@@ -2003,92 +2024,92 @@
         <v>21</v>
       </c>
       <c r="L22">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M22" t="s">
         <v>22</v>
       </c>
       <c r="N22" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="O22" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B23" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="E23" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F23" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G23" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="H23" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="I23" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K23" t="s">
         <v>21</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M23" t="s">
+        <v>22</v>
+      </c>
+      <c r="N23" t="s">
         <v>106</v>
       </c>
-      <c r="N23" t="s">
-        <v>101</v>
-      </c>
       <c r="O23" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E24" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F24" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G24" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H24" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="I24" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -2097,45 +2118,45 @@
         <v>21</v>
       </c>
       <c r="L24">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M24" t="s">
         <v>22</v>
       </c>
       <c r="N24" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="O24" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B25" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="E25" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F25" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="G25" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H25" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="I25" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J25">
         <v>2</v>
@@ -2144,45 +2165,45 @@
         <v>21</v>
       </c>
       <c r="L25">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M25" t="s">
         <v>22</v>
       </c>
       <c r="N25" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="O25" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D26" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="E26" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="F26" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="G26" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="H26" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="I26" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -2191,139 +2212,139 @@
         <v>21</v>
       </c>
       <c r="L26">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M26" t="s">
         <v>22</v>
       </c>
       <c r="N26" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="O26" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E27" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="F27" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G27" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="H27" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="I27" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="K27" t="s">
         <v>21</v>
       </c>
       <c r="L27">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M27" t="s">
         <v>22</v>
       </c>
       <c r="N27" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="O27" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E28" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="F28" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G28" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H28" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="I28" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="J28">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K28" t="s">
         <v>21</v>
       </c>
       <c r="L28">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="N28" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="O28" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="C29" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="D29" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E29" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F29" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="G29" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="H29" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="I29" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="J29">
         <v>2</v>
@@ -2332,92 +2353,92 @@
         <v>21</v>
       </c>
       <c r="L29">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s">
         <v>22</v>
       </c>
       <c r="N29" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="O29" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B30" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="C30" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="D30" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="E30" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="F30" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="G30" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="H30" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="I30" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="J30">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K30" t="s">
         <v>21</v>
       </c>
       <c r="L30">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M30" t="s">
         <v>22</v>
       </c>
       <c r="N30" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="O30" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="B31" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="D31" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="E31" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="F31" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="G31" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="H31" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="I31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J31">
         <v>2</v>
@@ -2426,45 +2447,45 @@
         <v>21</v>
       </c>
       <c r="L31">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M31" t="s">
         <v>22</v>
       </c>
       <c r="N31" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="O31" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="D32" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="E32" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="F32" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="G32" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="H32" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="I32" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J32">
         <v>2</v>
@@ -2476,42 +2497,42 @@
         <v>180</v>
       </c>
       <c r="M32" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="N32" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="O32" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="B33" t="s">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c r="D33" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="E33" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="F33" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="G33" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="H33" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="I33" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="J33">
         <v>2</v>
@@ -2523,42 +2544,42 @@
         <v>270</v>
       </c>
       <c r="M33" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="N33" t="s">
-        <v>139</v>
+        <v>171</v>
       </c>
       <c r="O33" t="s">
-        <v>139</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c r="D34" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="E34" t="s">
-        <v>127</v>
+        <v>174</v>
       </c>
       <c r="F34" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="G34" t="s">
-        <v>127</v>
+        <v>174</v>
       </c>
       <c r="H34" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="I34" t="s">
-        <v>128</v>
+        <v>174</v>
       </c>
       <c r="J34">
         <v>2</v>
@@ -2567,45 +2588,45 @@
         <v>21</v>
       </c>
       <c r="L34">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M34" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="N34" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="O34" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="B35" t="s">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c r="D35" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="E35" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F35" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="G35" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="H35" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="I35" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="J35">
         <v>2</v>
@@ -2614,48 +2635,48 @@
         <v>21</v>
       </c>
       <c r="L35">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M35" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="N35" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="O35" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="B36" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C36" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D36" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="E36" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F36" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="G36" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="H36" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="I36" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="J36">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="K36" t="s">
         <v>21</v>
@@ -2664,89 +2685,89 @@
         <v>0</v>
       </c>
       <c r="M36" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="N36" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="O36" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="B37" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C37" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D37" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="E37" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="F37" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="G37" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="H37" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="I37" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="J37">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K37" t="s">
         <v>21</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M37" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="N37" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="O37" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C38" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D38" t="s">
-        <v>174</v>
+        <v>51</v>
       </c>
       <c r="E38" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="F38" t="s">
-        <v>174</v>
+        <v>51</v>
       </c>
       <c r="G38" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="H38" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="I38" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="J38">
         <v>2</v>
@@ -2758,89 +2779,89 @@
         <v>0</v>
       </c>
       <c r="M38" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="N38" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="O38" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B39" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="C39" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="D39" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="F39" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="G39" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="H39" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="I39" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="J39">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K39" t="s">
         <v>21</v>
       </c>
       <c r="L39">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M39" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="N39" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="O39" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B40" t="s">
-        <v>124</v>
+        <v>194</v>
       </c>
       <c r="C40" t="s">
-        <v>125</v>
+        <v>195</v>
       </c>
       <c r="D40" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="E40" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="F40" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="G40" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="H40" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="I40" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="J40">
         <v>2</v>
@@ -2849,45 +2870,45 @@
         <v>21</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M40" t="s">
         <v>22</v>
       </c>
       <c r="N40" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="O40" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="B41" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C41" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D41" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="E41" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="G41" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
       <c r="H41" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="I41" t="s">
-        <v>195</v>
+        <v>19</v>
       </c>
       <c r="J41">
         <v>2</v>
@@ -2896,16 +2917,16 @@
         <v>21</v>
       </c>
       <c r="L41">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="N41" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="O41" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
